--- a/E/JAM01N.xlsx
+++ b/E/JAM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="75">
   <si>
     <t/>
   </si>
@@ -212,12 +212,6 @@
   </si>
   <si>
     <t>CERES DBL HZLNUT 350</t>
-  </si>
-  <si>
-    <t>20109980</t>
-  </si>
-  <si>
-    <t>OVOMALTINE BTL 230G</t>
   </si>
   <si>
     <t>20053052</t>
@@ -634,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1218,10 +1212,10 @@
         <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1238,10 +1232,10 @@
         <v>47</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1258,10 +1252,10 @@
         <v>47</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1278,29 +1272,9 @@
         <v>47</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F33" s="1" t="s">
         <v>38</v>
       </c>
     </row>
